--- a/Excel/Tính sản xuất năm 2026.xlsx
+++ b/Excel/Tính sản xuất năm 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vdm-fsvr\Du lieu dung chung VDM\PROJECT-IT HOA NGHIEP VU\Báo Cáo Hằng Ngày CK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_cokhi\Bao_Cao_Tu_Dong_PPTX_New\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F129D6-75E7-43E3-B2C8-0070B96CAB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33D9AC7-CC41-4F06-B835-DD9D05C7241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{B3516450-A8E9-41B1-B7A2-E64D853E5688}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{B3516450-A8E9-41B1-B7A2-E64D853E5688}"/>
   </bookViews>
   <sheets>
     <sheet name="NĂM 2026" sheetId="1" r:id="rId1"/>

--- a/Excel/Tính sản xuất năm 2026.xlsx
+++ b/Excel/Tính sản xuất năm 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code_cokhi\Bao_Cao_Tu_Dong_PPTX_New\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33D9AC7-CC41-4F06-B835-DD9D05C7241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7D01A8-AD34-4748-AD36-D0B1399B8C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{B3516450-A8E9-41B1-B7A2-E64D853E5688}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{B3516450-A8E9-41B1-B7A2-E64D853E5688}"/>
   </bookViews>
   <sheets>
     <sheet name="NĂM 2026" sheetId="1" r:id="rId1"/>
@@ -5535,30 +5535,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32057AB2-B1DC-4EB6-BFBA-69CD28D80819}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U159"/>
-  <sheetFormatPr defaultColWidth="10.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="10.5546875" style="1"/>
+    <col min="22" max="16384" width="10.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>2.3440212779844658</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>2.3780300781636488</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>2.3563290002469635</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>2.367670669481833</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>2.3833019482871007</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>2.3568280715776386</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>2.3727862142038267</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>2.4046991198547358</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>2.3997934737711692</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>2.3877325607211053</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>1</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>2.4118316505325978</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>0</v>
       </c>
@@ -6031,12 +6031,12 @@
         <v>2.4268760268194129</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>50.531016107647758</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>53.249029710638794</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>30</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>24.563776392143147</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>28</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>47.387640245927741</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>107.05370820253337</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>89.145709367104402</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>11.397601604768159</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>31</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>25</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>23</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>20</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
@@ -6361,7 +6361,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>19</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>11</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>10</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>9</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>8</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>7</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>6</v>
       </c>
@@ -6795,7 +6795,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>4</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>3</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>2</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>1</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>0</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>75.261103433630751</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>21</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>19</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>11</v>
       </c>
@@ -7307,7 +7307,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>10</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>9</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>8</v>
       </c>
@@ -7499,7 +7499,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>7</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>6</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>4</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>3</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>2</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>1</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>0</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>5.2297974648113588</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>21</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>19</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>11</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>10</v>
       </c>
@@ -8203,7 +8203,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>9</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>8</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>7</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>6</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>4</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>3</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>2</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>1</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>0</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>35.737393770387847</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>21</v>
       </c>
@@ -8857,7 +8857,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>19</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>11</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>10</v>
       </c>
@@ -9035,7 +9035,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>9</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>8</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>7</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>6</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>4</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>3</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>2</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>1</v>
       </c>
@@ -9611,7 +9611,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>0</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>65.019704076171124</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>21</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
         <v>19</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>11</v>
       </c>
@@ -9803,7 +9803,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>10</v>
       </c>
@@ -9867,7 +9867,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>9</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>8</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>7</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>6</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>4</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>3</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>2</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>1</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>0</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>5.2298253252797497</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>21</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
         <v>19</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>11</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>10</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>9</v>
       </c>
@@ -10763,7 +10763,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>8</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>7</v>
       </c>
@@ -10891,7 +10891,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>6</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -11019,7 +11019,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>4</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>3</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>2</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>1</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>0</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>13.69415419178058</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>21</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
         <v>19</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>11</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>10</v>
       </c>
@@ -11531,7 +11531,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>9</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="145" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>8</v>
       </c>
@@ -11659,7 +11659,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>7</v>
       </c>
@@ -11723,7 +11723,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>6</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>4</v>
       </c>
@@ -11915,7 +11915,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>3</v>
       </c>
@@ -11979,7 +11979,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>2</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>1</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>0</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>55.81169333941552</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="13" t="s">
         <v>47</v>
       </c>
@@ -12188,7 +12188,7 @@
       <c r="L156" s="13"/>
       <c r="M156" s="13"/>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="10" t="s">
         <v>44</v>
       </c>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
         <v>45</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>46</v>
       </c>
